--- a/Tables/B/G_EpisodeInfoTable.xlsx
+++ b/Tables/B/G_EpisodeInfoTable.xlsx
@@ -367,7 +367,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
+    <col customWidth="1" min="1" max="26" width="12.63"/>
   </cols>
   <sheetData/>
   <drawing r:id="rId1"/>
@@ -381,10 +381,24 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="15" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="9.38"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="2.63"/>
+    <col customWidth="1" min="6" max="7" width="6.13"/>
+    <col customWidth="1" min="8" max="8" width="7.0"/>
+    <col customWidth="1" min="9" max="9" width="8.63"/>
+    <col customWidth="1" min="10" max="10" width="7.25"/>
+    <col customWidth="1" min="11" max="11" width="11.25"/>
+    <col customWidth="1" min="12" max="12" width="10.88"/>
+    <col customWidth="1" min="13" max="13" width="10.63"/>
+    <col customWidth="1" min="14" max="14" width="9.13"/>
+    <col customWidth="1" min="15" max="15" width="12.63"/>
     <col customWidth="1" min="16" max="16" width="12.75"/>
     <col customWidth="1" min="17" max="17" width="17.63"/>
     <col customWidth="1" min="18" max="18" width="17.88"/>
+    <col customWidth="1" min="19" max="28" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7067,10 +7081,24 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="15" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="9.38"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="2.63"/>
+    <col customWidth="1" min="6" max="7" width="6.13"/>
+    <col customWidth="1" min="8" max="8" width="7.0"/>
+    <col customWidth="1" min="9" max="9" width="8.63"/>
+    <col customWidth="1" min="10" max="10" width="7.25"/>
+    <col customWidth="1" min="11" max="11" width="11.25"/>
+    <col customWidth="1" min="12" max="12" width="10.88"/>
+    <col customWidth="1" min="13" max="13" width="10.63"/>
+    <col customWidth="1" min="14" max="14" width="9.13"/>
+    <col customWidth="1" min="15" max="15" width="12.63"/>
     <col customWidth="1" min="16" max="16" width="12.75"/>
     <col customWidth="1" min="17" max="17" width="17.63"/>
     <col customWidth="1" min="18" max="18" width="17.88"/>
+    <col customWidth="1" min="19" max="28" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16093,10 +16121,24 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="15" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="9.38"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="2.63"/>
+    <col customWidth="1" min="6" max="7" width="6.13"/>
+    <col customWidth="1" min="8" max="8" width="7.0"/>
+    <col customWidth="1" min="9" max="9" width="8.63"/>
+    <col customWidth="1" min="10" max="10" width="7.25"/>
+    <col customWidth="1" min="11" max="11" width="11.25"/>
+    <col customWidth="1" min="12" max="12" width="10.88"/>
+    <col customWidth="1" min="13" max="13" width="10.63"/>
+    <col customWidth="1" min="14" max="14" width="9.13"/>
+    <col customWidth="1" min="15" max="15" width="12.63"/>
     <col customWidth="1" min="16" max="16" width="12.75"/>
     <col customWidth="1" min="17" max="17" width="17.63"/>
     <col customWidth="1" min="18" max="18" width="17.88"/>
+    <col customWidth="1" min="19" max="28" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
